--- a/fhir/StructureDefinition-ehealth-material-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-material-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,7 +352,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -734,7 +734,7 @@
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
 </t>
   </si>
   <si>
@@ -772,7 +772,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -807,7 +807,7 @@
     <t>Communication.inResponseTo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Communication)
+    <t xml:space="preserve">Reference(Communication|4.0.1)
 </t>
   </si>
   <si>
@@ -867,7 +867,7 @@
     <t>Codes for the reason why a communication did not happen.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/communication-not-done-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/communication-not-done-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -937,7 +937,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -968,7 +968,7 @@
     <t>Codes describing the purpose or content of the communication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/communication-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/communication-topic|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.context</t>
@@ -989,7 +989,7 @@
     <t>Communication.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1058,7 +1058,7 @@
     <t>Communication.sender</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson|HealthcareService)
+    <t xml:space="preserve">Reference(Device|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|HealthcareService|4.0.1)
 </t>
   </si>
   <si>
@@ -1083,7 +1083,7 @@
     <t>Codes for describing reasons for the occurrence of a communication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1098,7 +1098,7 @@
     <t>Communication.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>

--- a/fhir/StructureDefinition-ehealth-material-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-material-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-material-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-material-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-material-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-material-communication.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="375">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -511,6 +511,12 @@
   </si>
   <si>
     <t>function</t>
+  </si>
+  <si>
+    <t>The function of the participant</t>
+  </si>
+  <si>
+    <t>The code defining the function of the participant.</t>
   </si>
   <si>
     <t>Communication.extension:participant.extension:function.id</t>
@@ -2880,10 +2886,10 @@
         <v>130</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2960,10 +2966,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3069,10 +3075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3178,10 +3184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3207,13 +3213,13 @@
         <v>98</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3263,7 +3269,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>84</v>
@@ -3289,10 +3295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3315,13 +3321,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3348,11 +3354,11 @@
         <v>74</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -3370,7 +3376,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -3396,13 +3402,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>151</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>74</v>
@@ -3427,10 +3433,10 @@
         <v>130</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3507,10 +3513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3616,10 +3622,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3725,10 +3731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3754,13 +3760,13 @@
         <v>98</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3768,7 +3774,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>74</v>
@@ -3810,7 +3816,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>84</v>
@@ -3836,10 +3842,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3862,13 +3868,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3919,7 +3925,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3945,13 +3951,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>151</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>74</v>
@@ -3976,10 +3982,10 @@
         <v>130</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4056,10 +4062,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4165,10 +4171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4274,10 +4280,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4303,13 +4309,13 @@
         <v>98</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4317,7 +4323,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>74</v>
@@ -4359,7 +4365,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>84</v>
@@ -4385,10 +4391,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4414,10 +4420,10 @@
         <v>145</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4468,7 +4474,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4494,10 +4500,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4523,13 +4529,13 @@
         <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4537,7 +4543,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>74</v>
@@ -4579,7 +4585,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -4605,10 +4611,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4631,13 +4637,13 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4688,7 +4694,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4714,13 +4720,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>128</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>74</v>
@@ -4742,13 +4748,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4820,12 +4826,12 @@
         <v>74</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>144</v>
@@ -4934,7 +4940,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>151</v>
@@ -5043,10 +5049,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5072,13 +5078,13 @@
         <v>98</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5086,7 +5092,7 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>74</v>
@@ -5128,7 +5134,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>84</v>
@@ -5154,10 +5160,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5180,13 +5186,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5237,7 +5243,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5263,13 +5269,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>128</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>74</v>
@@ -5291,13 +5297,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5374,10 +5380,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5403,16 +5409,16 @@
         <v>130</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>155</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>74</v>
@@ -5461,7 +5467,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -5487,10 +5493,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5513,19 +5519,19 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -5574,7 +5580,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -5589,10 +5595,10 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>74</v>
@@ -5600,10 +5606,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5626,13 +5632,13 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5683,7 +5689,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -5698,21 +5704,21 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5738,13 +5744,13 @@
         <v>98</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5794,7 +5800,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -5809,25 +5815,25 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5846,16 +5852,16 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5905,7 +5911,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5920,7 +5926,7 @@
         <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>74</v>
@@ -5931,14 +5937,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5957,13 +5963,13 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6014,7 +6020,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6029,7 +6035,7 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>74</v>
@@ -6040,10 +6046,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6066,13 +6072,13 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6123,7 +6129,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -6149,10 +6155,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6178,13 +6184,13 @@
         <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6210,13 +6216,13 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -6234,7 +6240,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -6249,10 +6255,10 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>74</v>
@@ -6260,14 +6266,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6286,16 +6292,16 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6321,13 +6327,13 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>74</v>
@@ -6345,7 +6351,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6360,7 +6366,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>74</v>
@@ -6371,10 +6377,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6397,16 +6403,16 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6432,11 +6438,11 @@
         <v>74</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>74</v>
@@ -6454,7 +6460,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6472,7 +6478,7 @@
         <v>74</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>74</v>
@@ -6480,10 +6486,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6509,20 +6515,20 @@
         <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q46" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="R46" t="s" s="2">
         <v>74</v>
@@ -6543,13 +6549,13 @@
         <v>74</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>74</v>
@@ -6567,7 +6573,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -6585,7 +6591,7 @@
         <v>74</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>74</v>
@@ -6593,10 +6599,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6619,13 +6625,13 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6652,13 +6658,13 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>74</v>
@@ -6676,7 +6682,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
@@ -6702,14 +6708,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6728,13 +6734,13 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6785,7 +6791,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -6800,10 +6806,10 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>74</v>
@@ -6811,10 +6817,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6837,16 +6843,16 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6872,13 +6878,13 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6896,7 +6902,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -6914,7 +6920,7 @@
         <v>74</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>74</v>
@@ -6922,10 +6928,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6948,16 +6954,16 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7007,7 +7013,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7025,7 +7031,7 @@
         <v>74</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>74</v>
@@ -7033,10 +7039,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7059,16 +7065,16 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7118,7 +7124,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7133,10 +7139,10 @@
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>74</v>
@@ -7144,10 +7150,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7170,13 +7176,13 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7227,7 +7233,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -7242,10 +7248,10 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>74</v>
@@ -7253,10 +7259,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7279,13 +7285,13 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7336,7 +7342,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7351,10 +7357,10 @@
         <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>74</v>
@@ -7362,10 +7368,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7388,13 +7394,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7445,7 +7451,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -7460,10 +7466,10 @@
         <v>96</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>74</v>
@@ -7471,10 +7477,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7497,13 +7503,13 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7554,7 +7560,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -7569,10 +7575,10 @@
         <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>74</v>
@@ -7580,10 +7586,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7606,16 +7612,16 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7641,13 +7647,13 @@
         <v>74</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>74</v>
@@ -7665,7 +7671,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7680,21 +7686,21 @@
         <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7717,13 +7723,13 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7774,7 +7780,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -7789,21 +7795,21 @@
         <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7826,13 +7832,13 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7883,7 +7889,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -7909,10 +7915,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8018,10 +8024,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8129,14 +8135,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8158,16 +8164,16 @@
         <v>130</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>155</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>74</v>
@@ -8216,7 +8222,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8242,10 +8248,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8268,13 +8274,13 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8325,7 +8331,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -8351,10 +8357,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8377,13 +8383,13 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8434,7 +8440,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -8449,7 +8455,7 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>74</v>

--- a/fhir/StructureDefinition-ehealth-material-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-material-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-material-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-material-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-material-communication.xlsx
+++ b/fhir/StructureDefinition-ehealth-material-communication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
